--- a/Meta.xlsx
+++ b/Meta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{254E7553-123F-4AD1-B0CB-7E5456CB1D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43A363B-39CD-434D-B984-3FBE11CA701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{2E7EBCAC-6036-43C0-BFEE-816C31250952}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{2E7EBCAC-6036-43C0-BFEE-816C31250952}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1044,13 +1044,19 @@
     <numFmt numFmtId="171" formatCode="&quot;FY&quot;0&quot;A&quot;"/>
     <numFmt numFmtId="172" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1377,139 +1383,142 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="18" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2019,7 +2028,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="3">
-        <v>606.92999999999995</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2027,11 +2036,11 @@
         <v>6</v>
       </c>
       <c r="I3" s="4">
-        <f>2196.045588+342.377716</f>
-        <v>2538.4233039999999</v>
-      </c>
-      <c r="J3" s="81" t="s">
-        <v>306</v>
+        <f>2205.128509+342.377716</f>
+        <v>2547.5062250000001</v>
+      </c>
+      <c r="J3" s="82" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2043,7 +2052,7 @@
       </c>
       <c r="I4" s="4">
         <f>I2*I3</f>
-        <v>1540645.2558967199</v>
+        <v>1362915.8303750001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2054,11 +2063,11 @@
         <v>8</v>
       </c>
       <c r="I5" s="4">
-        <f>23426+57754</f>
-        <v>81180</v>
-      </c>
-      <c r="J5" s="81" t="s">
-        <v>306</v>
+        <f>15462+74798</f>
+        <v>90260</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2068,10 +2077,10 @@
         <v>9</v>
       </c>
       <c r="I6" s="4">
-        <v>58748</v>
-      </c>
-      <c r="J6" s="81" t="s">
-        <v>306</v>
+        <v>83664</v>
+      </c>
+      <c r="J6" s="82" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2086,7 +2095,7 @@
       </c>
       <c r="I7" s="4">
         <f>I4-I5+I6</f>
-        <v>1518213.2558967199</v>
+        <v>1356319.8303750001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2256,16 +2265,16 @@
       <c r="N2" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="O2" s="81" t="s">
+      <c r="O2" s="75" t="s">
         <v>306</v>
       </c>
-      <c r="P2" s="81" t="s">
+      <c r="P2" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="Q2" s="81" t="s">
+      <c r="Q2" s="75" t="s">
         <v>308</v>
       </c>
-      <c r="R2" s="81" t="s">
+      <c r="R2" s="75" t="s">
         <v>309</v>
       </c>
       <c r="T2" s="5" t="s">
@@ -2336,7 +2345,9 @@
       <c r="O3" s="10">
         <v>3.56</v>
       </c>
-      <c r="P3" s="10"/>
+      <c r="P3" s="10">
+        <v>3.6</v>
+      </c>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="10"/>
@@ -2421,7 +2432,10 @@
         <f t="shared" si="1"/>
         <v>15.704775280898877</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <f t="shared" si="1"/>
+        <v>16.769444444444446</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="10"/>
@@ -2501,7 +2515,9 @@
       <c r="O5" s="11">
         <v>0.19</v>
       </c>
-      <c r="P5" s="11"/>
+      <c r="P5" s="11">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
       <c r="S5" s="10"/>
@@ -2573,7 +2589,9 @@
       <c r="O6" s="11">
         <v>0.12</v>
       </c>
-      <c r="P6" s="11"/>
+      <c r="P6" s="11">
+        <v>0.12</v>
+      </c>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
       <c r="S6" s="4"/>
@@ -2667,13 +2685,15 @@
         <v>50082</v>
       </c>
       <c r="N8" s="4">
-        <f>+AA8-SUM(K8:M8)</f>
+        <f t="shared" ref="N8:N13" si="2">+AA8-SUM(K8:M8)</f>
         <v>58138</v>
       </c>
       <c r="O8" s="4">
         <v>55024</v>
       </c>
-      <c r="P8" s="4"/>
+      <c r="P8" s="4">
+        <v>59363</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -2820,7 +2840,7 @@
         <v>293</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" ref="F9:F21" si="2">+Y9-SUM(C9:E9)</f>
+        <f t="shared" ref="F9:F21" si="3">+Y9-SUM(C9:E9)</f>
         <v>335</v>
       </c>
       <c r="G9" s="4">
@@ -2833,7 +2853,7 @@
         <v>434</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" ref="J9:J21" si="3">+Z9-SUM(G9:I9)</f>
+        <f t="shared" ref="J9:J21" si="4">+Z9-SUM(G9:I9)</f>
         <v>519</v>
       </c>
       <c r="K9" s="4">
@@ -2846,13 +2866,15 @@
         <v>690</v>
       </c>
       <c r="N9" s="4">
-        <f>+AA9-SUM(K9:M9)</f>
+        <f t="shared" si="2"/>
         <v>801</v>
       </c>
       <c r="O9" s="4">
         <v>885</v>
       </c>
-      <c r="P9" s="4"/>
+      <c r="P9" s="4">
+        <v>1007</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -2999,7 +3021,7 @@
         <v>3396</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69581</v>
       </c>
       <c r="G10" s="4">
@@ -3012,7 +3034,7 @@
         <v>40319</v>
       </c>
       <c r="J10" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>47303</v>
       </c>
       <c r="K10" s="4">
@@ -3025,13 +3047,15 @@
         <v>50772</v>
       </c>
       <c r="N10" s="4">
-        <f>+AA10-SUM(K10:M10)</f>
+        <f t="shared" si="2"/>
         <v>58939</v>
       </c>
       <c r="O10" s="4">
         <v>55909</v>
       </c>
-      <c r="P10" s="4"/>
+      <c r="P10" s="4">
+        <v>60370</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -3178,7 +3202,7 @@
         <v>210</v>
       </c>
       <c r="F11" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1929</v>
       </c>
       <c r="G11" s="4">
@@ -3191,7 +3215,7 @@
         <v>270</v>
       </c>
       <c r="J11" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1083</v>
       </c>
       <c r="K11" s="4">
@@ -3204,13 +3228,15 @@
         <v>470</v>
       </c>
       <c r="N11" s="4">
-        <f>+AA11-SUM(K11:M11)</f>
+        <f t="shared" si="2"/>
         <v>955</v>
       </c>
       <c r="O11" s="4">
         <v>402</v>
       </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4">
+        <v>431</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -3357,7 +3383,7 @@
         <v>34146</v>
       </c>
       <c r="F12" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40112</v>
       </c>
       <c r="G12" s="13">
@@ -3370,7 +3396,7 @@
         <v>40589</v>
       </c>
       <c r="J12" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>48386</v>
       </c>
       <c r="K12" s="13">
@@ -3383,13 +3409,15 @@
         <v>51242</v>
       </c>
       <c r="N12" s="13">
-        <f>+AA12-SUM(K12:M12)</f>
+        <f t="shared" si="2"/>
         <v>59894</v>
       </c>
       <c r="O12" s="13">
         <v>56311</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13">
+        <v>60801</v>
+      </c>
       <c r="Q12" s="13"/>
       <c r="R12" s="13"/>
       <c r="S12" s="4"/>
@@ -3425,27 +3453,27 @@
         <v>225524.40408825368</v>
       </c>
       <c r="AD12" s="13">
-        <f t="shared" ref="AD12:AI12" si="4">+AC12*(1+AD28)</f>
+        <f t="shared" ref="AD12:AI12" si="5">+AC12*(1+AD28)</f>
         <v>236935.78227574998</v>
       </c>
       <c r="AE12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>247725.68967298549</v>
       </c>
       <c r="AF12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>257878.83540400601</v>
       </c>
       <c r="AG12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>267391.18456824945</v>
       </c>
       <c r="AH12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>276268.09172645857</v>
       </c>
       <c r="AI12" s="13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>284522.53580804681</v>
       </c>
       <c r="AJ12" s="4"/>
@@ -3559,7 +3587,7 @@
         <v>6210</v>
       </c>
       <c r="F13" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7696</v>
       </c>
       <c r="G13" s="4">
@@ -3572,7 +3600,7 @@
         <v>7375</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8838</v>
       </c>
       <c r="K13" s="4">
@@ -3585,13 +3613,15 @@
         <v>9206</v>
       </c>
       <c r="N13" s="4">
-        <f>+AA13-SUM(K13:M13)</f>
+        <f t="shared" si="2"/>
         <v>10906</v>
       </c>
       <c r="O13" s="4">
         <v>10218</v>
       </c>
-      <c r="P13" s="4"/>
+      <c r="P13" s="4">
+        <v>11330</v>
+      </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -3729,7 +3759,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:G14" si="5">C12-C13</f>
+        <f t="shared" ref="C14:G14" si="6">C12-C13</f>
         <v>22537</v>
       </c>
       <c r="D14" s="4">
@@ -3737,15 +3767,15 @@
         <v>26054</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>27936</v>
       </c>
       <c r="F14" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>32416</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>29815</v>
       </c>
       <c r="H14" s="4">
@@ -3753,67 +3783,70 @@
         <v>31763</v>
       </c>
       <c r="I14" s="4">
-        <f t="shared" ref="I14:AA14" si="6">I12-I13</f>
+        <f t="shared" ref="I14:AA14" si="7">I12-I13</f>
         <v>33214</v>
       </c>
       <c r="J14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>39548</v>
       </c>
       <c r="K14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>34742</v>
       </c>
       <c r="L14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>39025</v>
       </c>
       <c r="M14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>42036</v>
       </c>
       <c r="N14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48988</v>
       </c>
       <c r="O14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46093</v>
       </c>
-      <c r="P14" s="4"/>
+      <c r="P14" s="4">
+        <f t="shared" si="7"/>
+        <v>49471</v>
+      </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46483</v>
       </c>
       <c r="U14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>57927</v>
       </c>
       <c r="V14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>69273</v>
       </c>
       <c r="W14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>95280</v>
       </c>
       <c r="X14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>91360</v>
       </c>
       <c r="Y14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>108943</v>
       </c>
       <c r="Z14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>134340</v>
       </c>
       <c r="AA14" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>164791</v>
       </c>
       <c r="AB14" s="4"/>
@@ -3935,7 +3968,7 @@
         <v>9241</v>
       </c>
       <c r="F15" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10517</v>
       </c>
       <c r="G15" s="4">
@@ -3948,7 +3981,7 @@
         <v>11177</v>
       </c>
       <c r="J15" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12181</v>
       </c>
       <c r="K15" s="4">
@@ -3967,7 +4000,9 @@
       <c r="O15" s="4">
         <v>17699</v>
       </c>
-      <c r="P15" s="4"/>
+      <c r="P15" s="4">
+        <v>21656</v>
+      </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -4114,7 +4149,7 @@
         <v>2877</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3226</v>
       </c>
       <c r="G16" s="4">
@@ -4127,7 +4162,7 @@
         <v>2822</v>
       </c>
       <c r="J16" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3240</v>
       </c>
       <c r="K16" s="4">
@@ -4146,7 +4181,9 @@
       <c r="O16" s="4">
         <v>2908</v>
       </c>
-      <c r="P16" s="4"/>
+      <c r="P16" s="4">
+        <v>3431</v>
+      </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -4293,7 +4330,7 @@
         <v>2070</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2289</v>
       </c>
       <c r="G17" s="4">
@@ -4306,7 +4343,7 @@
         <v>1865</v>
       </c>
       <c r="J17" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>762</v>
       </c>
       <c r="K17" s="4">
@@ -4325,7 +4362,9 @@
       <c r="O17" s="4">
         <v>2614</v>
       </c>
-      <c r="P17" s="4"/>
+      <c r="P17" s="4">
+        <v>5609</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -4463,7 +4502,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" ref="C18:G18" si="7">C14-SUM(C15:C17)</f>
+        <f t="shared" ref="C18:G18" si="8">C14-SUM(C15:C17)</f>
         <v>7227</v>
       </c>
       <c r="D18" s="4">
@@ -4471,15 +4510,15 @@
         <v>9392</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13748</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16384</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13818</v>
       </c>
       <c r="H18" s="4">
@@ -4487,67 +4526,70 @@
         <v>14847</v>
       </c>
       <c r="I18" s="4">
-        <f t="shared" ref="I18:AA18" si="8">I14-SUM(I15:I17)</f>
+        <f t="shared" ref="I18:AA18" si="9">I14-SUM(I15:I17)</f>
         <v>17350</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>23365</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17555</v>
       </c>
       <c r="L18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20441</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20535</v>
       </c>
       <c r="N18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>24745</v>
       </c>
       <c r="O18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>22872</v>
       </c>
-      <c r="P18" s="4"/>
+      <c r="P18" s="4">
+        <f t="shared" si="9"/>
+        <v>18775</v>
+      </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>24913</v>
       </c>
       <c r="U18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>23986</v>
       </c>
       <c r="V18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>32671</v>
       </c>
       <c r="W18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46753</v>
       </c>
       <c r="X18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>28944</v>
       </c>
       <c r="Y18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46751</v>
       </c>
       <c r="Z18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>69380</v>
       </c>
       <c r="AA18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>83276</v>
       </c>
       <c r="AB18" s="4"/>
@@ -4669,7 +4711,7 @@
         <v>272</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>424</v>
       </c>
       <c r="G19" s="4">
@@ -4682,7 +4724,7 @@
         <v>472</v>
       </c>
       <c r="J19" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>187</v>
       </c>
       <c r="K19" s="4">
@@ -4701,7 +4743,9 @@
       <c r="O19" s="4">
         <v>-1120</v>
       </c>
-      <c r="P19" s="4"/>
+      <c r="P19" s="4">
+        <v>-19</v>
+      </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -4839,91 +4883,94 @@
         <v>27</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20:O20" si="9">C18+C19</f>
+        <f t="shared" ref="C20:P20" si="10">C18+C19</f>
         <v>7307</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>9293</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14020</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>16808</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14183</v>
       </c>
       <c r="H20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>15106</v>
       </c>
       <c r="I20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>17822</v>
       </c>
       <c r="J20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>23552</v>
       </c>
       <c r="K20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>18382</v>
       </c>
       <c r="L20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>20534</v>
       </c>
       <c r="M20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21663</v>
       </c>
       <c r="N20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>25353</v>
       </c>
       <c r="O20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21752</v>
       </c>
-      <c r="P20" s="4"/>
+      <c r="P20" s="4">
+        <f t="shared" si="10"/>
+        <v>18756</v>
+      </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4">
-        <f t="shared" ref="T20:AA20" si="10">T18+T19</f>
+        <f t="shared" ref="T20:AA20" si="11">T18+T19</f>
         <v>25361</v>
       </c>
       <c r="U20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>24812</v>
       </c>
       <c r="V20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>33180</v>
       </c>
       <c r="W20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>47284</v>
       </c>
       <c r="X20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28819</v>
       </c>
       <c r="Y20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>47428</v>
       </c>
       <c r="Z20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>70663</v>
       </c>
       <c r="AA20" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>85932</v>
       </c>
       <c r="AB20" s="4"/>
@@ -5045,7 +5092,7 @@
         <v>2437</v>
       </c>
       <c r="F21" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2790</v>
       </c>
       <c r="G21" s="4">
@@ -5058,7 +5105,7 @@
         <v>2134</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2714</v>
       </c>
       <c r="K21" s="4">
@@ -5077,7 +5124,9 @@
       <c r="O21" s="4">
         <v>-5021</v>
       </c>
-      <c r="P21" s="4"/>
+      <c r="P21" s="4">
+        <v>2908</v>
+      </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -5216,7 +5265,7 @@
         <v>30</v>
       </c>
       <c r="C22" s="4">
-        <f t="shared" ref="C22:F22" si="11">C20-C21</f>
+        <f t="shared" ref="C22:F22" si="12">C20-C21</f>
         <v>5709</v>
       </c>
       <c r="D22" s="4">
@@ -5224,11 +5273,11 @@
         <v>7788</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>11583</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14018</v>
       </c>
       <c r="G22" s="4">
@@ -5240,67 +5289,70 @@
         <v>13465</v>
       </c>
       <c r="I22" s="4">
-        <f t="shared" ref="I22:AA22" si="12">I20-I21</f>
+        <f t="shared" ref="I22:AA22" si="13">I20-I21</f>
         <v>15688</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20838</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16644</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18337</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2709</v>
       </c>
       <c r="N22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22768</v>
       </c>
       <c r="O22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>26773</v>
       </c>
-      <c r="P22" s="4"/>
+      <c r="P22" s="4">
+        <f t="shared" si="13"/>
+        <v>15848</v>
+      </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22111</v>
       </c>
       <c r="U22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>18485</v>
       </c>
       <c r="V22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29146</v>
       </c>
       <c r="W22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39370</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23200</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39098</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>62360</v>
       </c>
       <c r="AA22" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>60458</v>
       </c>
       <c r="AB22" s="4"/>
@@ -5544,23 +5596,23 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <f t="shared" ref="C24:G24" si="13">C22/C25</f>
+        <f t="shared" ref="C24:G24" si="14">C22/C25</f>
         <v>2.206803247004252</v>
       </c>
       <c r="D24" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.0327102803738319</v>
       </c>
       <c r="E24" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.4965062111801242</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.4459984459984456</v>
       </c>
       <c r="G24" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8601178781925345</v>
       </c>
       <c r="H24" s="14">
@@ -5568,67 +5620,70 @@
         <v>5.3137332280978686</v>
       </c>
       <c r="I24" s="14">
-        <f t="shared" ref="I24:AA24" si="14">I22/I25</f>
+        <f t="shared" ref="I24:AA24" si="15">I22/I25</f>
         <v>6.2032423882957692</v>
       </c>
       <c r="J24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.2244681784391389</v>
       </c>
       <c r="K24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.5864661654135341</v>
       </c>
       <c r="L24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.2823669579030978</v>
       </c>
       <c r="M24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1.0762812872467222</v>
       </c>
       <c r="N24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.0313367711225698</v>
       </c>
       <c r="O24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.565509076558801</v>
       </c>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <f t="shared" si="15"/>
+        <v>6.2320094376720405</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="4"/>
       <c r="T24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.6508650519031143</v>
       </c>
       <c r="U24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.47687456201822</v>
       </c>
       <c r="V24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.223079621185549</v>
       </c>
       <c r="W24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>13.985790408525755</v>
       </c>
       <c r="X24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>8.6341644957201336</v>
       </c>
       <c r="Y24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.189588189588189</v>
       </c>
       <c r="Z24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24.609313338595108</v>
       </c>
       <c r="AA24" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.981753272510907</v>
       </c>
       <c r="AB24" s="4"/>
@@ -5780,7 +5835,9 @@
       <c r="O25" s="4">
         <v>2534</v>
       </c>
-      <c r="P25" s="4"/>
+      <c r="P25" s="4">
+        <v>2543</v>
+      </c>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
@@ -6053,64 +6110,67 @@
       <c r="E27" s="4"/>
       <c r="F27" s="11"/>
       <c r="G27" s="11">
-        <f t="shared" ref="G27:M27" si="15">G3/C3-1</f>
+        <f t="shared" ref="G27:M27" si="16">G3/C3-1</f>
         <v>7.2847682119205448E-2</v>
       </c>
       <c r="H27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.514657980456029E-2</v>
       </c>
       <c r="I27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>4.7770700636942554E-2</v>
       </c>
       <c r="J27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.0156739811912265E-2</v>
       </c>
       <c r="K27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>5.8641975308642014E-2</v>
       </c>
       <c r="L27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.4220183486238591E-2</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>7.5987841945288848E-2</v>
       </c>
       <c r="N27" s="11">
-        <f t="shared" ref="N27" si="16">N3/J3-1</f>
+        <f t="shared" ref="N27" si="17">N3/J3-1</f>
         <v>6.8656716417910379E-2</v>
       </c>
       <c r="O27" s="11">
-        <f t="shared" ref="O27" si="17">O3/K3-1</f>
+        <f t="shared" ref="O27:P27" si="18">O3/K3-1</f>
         <v>3.790087463556846E-2</v>
       </c>
-      <c r="P27" s="11"/>
+      <c r="P27" s="11">
+        <f t="shared" si="18"/>
+        <v>3.4482758620689724E-2</v>
+      </c>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="11">
-        <f t="shared" ref="U27:Y27" si="18">+U3/T3-1</f>
+        <f t="shared" ref="U27:Y27" si="19">+U3/T3-1</f>
         <v>0.11330049261083741</v>
       </c>
       <c r="V27" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.15044247787610643</v>
       </c>
       <c r="W27" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>8.4615384615384537E-2</v>
       </c>
       <c r="X27" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4.9645390070921946E-2</v>
       </c>
       <c r="Y27" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.7702702702702631E-2</v>
       </c>
       <c r="Z27" s="11">
@@ -6235,64 +6295,67 @@
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="15">
-        <f t="shared" ref="G28:M28" si="19">G12/C12-1</f>
+        <f t="shared" ref="G28:M28" si="20">G12/C12-1</f>
         <v>0.27264793157619138</v>
       </c>
       <c r="H28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.2210069064658271</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.18868974404029748</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.20627243717590749</v>
       </c>
       <c r="K28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.16071869428062002</v>
       </c>
       <c r="L28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.21614496685521223</v>
       </c>
       <c r="M28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.26246027248761972</v>
       </c>
       <c r="N28" s="15">
-        <f t="shared" ref="N28" si="20">N12/J12-1</f>
+        <f t="shared" ref="N28" si="21">N12/J12-1</f>
         <v>0.23783739098086221</v>
       </c>
       <c r="O28" s="15">
-        <f t="shared" ref="O28" si="21">O12/K12-1</f>
+        <f t="shared" ref="O28:P28" si="22">O12/K12-1</f>
         <v>0.33078886420570019</v>
       </c>
-      <c r="P28" s="11"/>
+      <c r="P28" s="15">
+        <f t="shared" si="22"/>
+        <v>0.27959003283104633</v>
+      </c>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="15">
-        <f t="shared" ref="U28:Y28" si="22">+U12/T12-1</f>
+        <f t="shared" ref="U28:Y28" si="23">+U12/T12-1</f>
         <v>0.26610910132884413</v>
       </c>
       <c r="V28" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.21596390228722573</v>
       </c>
       <c r="W28" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.37182574303495608</v>
       </c>
       <c r="X28" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-1.1193175554782941E-2</v>
       </c>
       <c r="Y28" s="15">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.15687468377226454</v>
       </c>
       <c r="Z28" s="15">
@@ -6304,7 +6367,7 @@
         <v>0.22167038498246217</v>
       </c>
       <c r="AB28" s="15">
-        <f t="shared" ref="AB28" si="23">+AB12/AA12-1</f>
+        <f t="shared" ref="AB28" si="24">+AB12/AA12-1</f>
         <v>6.2468278216215589E-2</v>
       </c>
       <c r="AC28" s="15">
@@ -6312,39 +6375,39 @@
         <v>5.622145039459403E-2</v>
       </c>
       <c r="AD28" s="15">
-        <f t="shared" ref="AD28:AL28" si="24">+AC28*(1-10%)</f>
+        <f t="shared" ref="AD28:AL28" si="25">+AC28*(1-10%)</f>
         <v>5.0599305355134627E-2</v>
       </c>
       <c r="AE28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.5539374819621163E-2</v>
       </c>
       <c r="AF28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.0985437337659046E-2</v>
       </c>
       <c r="AG28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.6886893603893141E-2</v>
       </c>
       <c r="AH28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.319820424350383E-2</v>
       </c>
       <c r="AI28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.9878383819153448E-2</v>
       </c>
       <c r="AJ28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.6890545437238105E-2</v>
       </c>
       <c r="AK28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.4201490893514296E-2</v>
       </c>
       <c r="AL28" s="15">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.1781341804162867E-2</v>
       </c>
       <c r="AM28" s="4"/>
@@ -6446,83 +6509,86 @@
         <v>33</v>
       </c>
       <c r="C29" s="11">
-        <f t="shared" ref="C29:J29" si="25">C14/C12</f>
+        <f t="shared" ref="C29:J29" si="26">C14/C12</f>
         <v>0.7867690696456624</v>
       </c>
       <c r="D29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81421294415450485</v>
       </c>
       <c r="E29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81813389562467054</v>
       </c>
       <c r="F29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.8081372157957718</v>
       </c>
       <c r="G29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81785763269784661</v>
       </c>
       <c r="H29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81295590079598679</v>
       </c>
       <c r="I29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81830052477272164</v>
       </c>
       <c r="J29" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.81734385979415536</v>
       </c>
       <c r="K29" s="11">
-        <f t="shared" ref="K29:L29" si="26">K14/K12</f>
+        <f t="shared" ref="K29:L29" si="27">K14/K12</f>
         <v>0.82105213404546962</v>
       </c>
       <c r="L29" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.82130229817324696</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" ref="M29:O29" si="27">M14/M12</f>
+        <f t="shared" ref="M29:O29" si="28">M14/M12</f>
         <v>0.82034268763904605</v>
       </c>
       <c r="N29" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.81791164390423077</v>
       </c>
       <c r="O29" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.8185434462183232</v>
       </c>
-      <c r="P29" s="11"/>
+      <c r="P29" s="11">
+        <f t="shared" ref="P29" si="29">P14/P12</f>
+        <v>0.81365438068452822</v>
+      </c>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
       <c r="S29" s="4"/>
       <c r="T29" s="11">
-        <f t="shared" ref="T29" si="28">+T14/T12</f>
+        <f t="shared" ref="T29" si="30">+T14/T12</f>
         <v>0.8324617643898421</v>
       </c>
       <c r="U29" s="11">
-        <f t="shared" ref="U29:Y29" si="29">+U14/U12</f>
+        <f t="shared" ref="U29:Y29" si="31">+U14/U12</f>
         <v>0.81936998741106415</v>
       </c>
       <c r="V29" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.80582795323678236</v>
       </c>
       <c r="W29" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.80794376277251567</v>
       </c>
       <c r="X29" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.78347297378418479</v>
       </c>
       <c r="Y29" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.8075714222176098</v>
       </c>
       <c r="Z29" s="11">
@@ -6643,83 +6709,86 @@
         <v>34</v>
       </c>
       <c r="C30" s="11">
-        <f t="shared" ref="C30:J30" si="30">C18/C12</f>
+        <f t="shared" ref="C30:J30" si="32">C18/C12</f>
         <v>0.25229533950078548</v>
       </c>
       <c r="D30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.29350917216163003</v>
       </c>
       <c r="E30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.40262402624026239</v>
       </c>
       <c r="F30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.40845632229756679</v>
       </c>
       <c r="G30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.37904265532848719</v>
       </c>
       <c r="H30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.38000051188861306</v>
       </c>
       <c r="I30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.4274557146024785</v>
       </c>
       <c r="J30" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.48288761211920805</v>
       </c>
       <c r="K30" s="11">
-        <f t="shared" ref="K30:L30" si="31">K18/K12</f>
+        <f t="shared" ref="K30:L30" si="33">K18/K12</f>
         <v>0.41487450961856598</v>
       </c>
       <c r="L30" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.43019193534809325</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" ref="M30:O30" si="32">M18/M12</f>
+        <f t="shared" ref="M30:O30" si="34">M18/M12</f>
         <v>0.4007454822216151</v>
       </c>
       <c r="N30" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.41314655892076002</v>
       </c>
       <c r="O30" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.40617286143027115</v>
       </c>
-      <c r="P30" s="11"/>
+      <c r="P30" s="11">
+        <f t="shared" ref="P30" si="35">P18/P12</f>
+        <v>0.30879426325224912</v>
+      </c>
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
       <c r="S30" s="4"/>
       <c r="T30" s="11">
-        <f t="shared" ref="T30" si="33">+T18/T12</f>
+        <f t="shared" ref="T30" si="36">+T18/T12</f>
         <v>0.44616569361366809</v>
       </c>
       <c r="U30" s="11">
-        <f t="shared" ref="U30:Y30" si="34">+U18/U12</f>
+        <f t="shared" ref="U30:Y30" si="37">+U18/U12</f>
         <v>0.33927889443682191</v>
       </c>
       <c r="V30" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.3800500203571221</v>
       </c>
       <c r="W30" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.39645040660058173</v>
       </c>
       <c r="X30" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.24821411726367604</v>
       </c>
       <c r="Y30" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="37"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="Z30" s="11">
@@ -6840,23 +6909,23 @@
         <v>35</v>
       </c>
       <c r="C31" s="11">
-        <f t="shared" ref="C31:G31" si="35">C21/C20</f>
+        <f t="shared" ref="C31:G31" si="38">C21/C20</f>
         <v>0.21869440262761736</v>
       </c>
       <c r="D31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.16194985472936618</v>
       </c>
       <c r="E31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.1738231098430813</v>
       </c>
       <c r="F31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.16599238457877202</v>
       </c>
       <c r="G31" s="11">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.12789959811041388</v>
       </c>
       <c r="H31" s="11">
@@ -6864,59 +6933,62 @@
         <v>0.10863233152389778</v>
       </c>
       <c r="I31" s="11">
-        <f t="shared" ref="I31:J31" si="36">I21/I20</f>
+        <f t="shared" ref="I31:J31" si="39">I21/I20</f>
         <v>0.11973964762652901</v>
       </c>
       <c r="J31" s="11">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.115234375</v>
       </c>
       <c r="K31" s="11">
-        <f t="shared" ref="K31:L31" si="37">K21/K20</f>
+        <f t="shared" ref="K31:L31" si="40">K21/K20</f>
         <v>9.4549015341094556E-2</v>
       </c>
       <c r="L31" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.10699327943897925</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" ref="M31:O31" si="38">M21/M20</f>
+        <f t="shared" ref="M31:O31" si="41">M21/M20</f>
         <v>0.87494806813460735</v>
       </c>
       <c r="N31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>0.10196032027767916</v>
       </c>
       <c r="O31" s="11">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>-0.23082934902537697</v>
       </c>
-      <c r="P31" s="11"/>
+      <c r="P31" s="11">
+        <f t="shared" ref="P31" si="42">P21/P20</f>
+        <v>0.15504371934314354</v>
+      </c>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
       <c r="S31" s="4"/>
       <c r="T31" s="11">
-        <f t="shared" ref="T31" si="39">+T21/T20</f>
+        <f t="shared" ref="T31" si="43">+T21/T20</f>
         <v>0.12814952091794488</v>
       </c>
       <c r="U31" s="11">
-        <f t="shared" ref="U31:Y31" si="40">+U21/U20</f>
+        <f t="shared" ref="U31:Y31" si="44">+U21/U20</f>
         <v>0.25499758181525067</v>
       </c>
       <c r="V31" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.12157926461723931</v>
       </c>
       <c r="W31" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.16737162676592504</v>
       </c>
       <c r="X31" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.19497553697213643</v>
       </c>
       <c r="Y31" s="11">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.17563464620055663</v>
       </c>
       <c r="Z31" s="11">
@@ -7785,27 +7857,27 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4">
-        <f t="shared" ref="T37:Y37" si="41">+SUM(T33:T36)</f>
+        <f t="shared" ref="T37:Y37" si="45">+SUM(T33:T36)</f>
         <v>50480</v>
       </c>
       <c r="U37" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>66225</v>
       </c>
       <c r="V37" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>75670</v>
       </c>
       <c r="W37" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>66666</v>
       </c>
       <c r="X37" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>59549</v>
       </c>
       <c r="Y37" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>85365</v>
       </c>
       <c r="Z37" s="4">
@@ -8698,27 +8770,27 @@
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
       <c r="T43" s="4">
-        <f t="shared" ref="T43:Y43" si="42">+SUM(T38:T42)</f>
+        <f t="shared" ref="T43:Y43" si="46">+SUM(T38:T42)</f>
         <v>46854</v>
       </c>
       <c r="U43" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>67151</v>
       </c>
       <c r="V43" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>83646</v>
       </c>
       <c r="W43" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>99321</v>
       </c>
       <c r="X43" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>126178</v>
       </c>
       <c r="Y43" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>144258</v>
       </c>
       <c r="Z43" s="4">
@@ -8856,27 +8928,27 @@
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="13">
-        <f t="shared" ref="T44:Y44" si="43">+T37+T43</f>
+        <f t="shared" ref="T44:Y44" si="47">+T37+T43</f>
         <v>97334</v>
       </c>
       <c r="U44" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>133376</v>
       </c>
       <c r="V44" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>159316</v>
       </c>
       <c r="W44" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>165987</v>
       </c>
       <c r="X44" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>185727</v>
       </c>
       <c r="Y44" s="13">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>229623</v>
       </c>
       <c r="Z44" s="13">
@@ -9472,23 +9544,23 @@
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
       <c r="T48" s="4">
-        <f t="shared" ref="T48:X48" si="44">+SUM(T45:T47)</f>
+        <f t="shared" ref="T48:X48" si="48">+SUM(T45:T47)</f>
         <v>7017</v>
       </c>
       <c r="U48" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>15053</v>
       </c>
       <c r="V48" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>14981</v>
       </c>
       <c r="W48" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>21135</v>
       </c>
       <c r="X48" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>27026</v>
       </c>
       <c r="Y48" s="4">
@@ -10230,19 +10302,19 @@
       <c r="R53" s="4"/>
       <c r="S53" s="4"/>
       <c r="T53" s="4">
-        <f t="shared" ref="T53:W53" si="45">+SUM(T49:T52)</f>
+        <f t="shared" ref="T53:W53" si="49">+SUM(T49:T52)</f>
         <v>6190</v>
       </c>
       <c r="U53" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>17269</v>
       </c>
       <c r="V53" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>16045</v>
       </c>
       <c r="W53" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>19973</v>
       </c>
       <c r="X53" s="4">
@@ -10388,19 +10460,19 @@
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
       <c r="T54" s="13">
-        <f t="shared" ref="T54:W54" si="46">+T48+T53</f>
+        <f t="shared" ref="T54:W54" si="50">+T48+T53</f>
         <v>13207</v>
       </c>
       <c r="U54" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>32322</v>
       </c>
       <c r="V54" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>31026</v>
       </c>
       <c r="W54" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>41108</v>
       </c>
       <c r="X54" s="13">
@@ -10696,23 +10768,23 @@
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
       <c r="T56" s="13">
-        <f t="shared" ref="T56:X56" si="47">+T54+T55</f>
+        <f t="shared" ref="T56:X56" si="51">+T54+T55</f>
         <v>97334</v>
       </c>
       <c r="U56" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>133376</v>
       </c>
       <c r="V56" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>159316</v>
       </c>
       <c r="W56" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>165987</v>
       </c>
       <c r="X56" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>185727</v>
       </c>
       <c r="Y56" s="13">
@@ -10989,23 +11061,23 @@
         <v>22112</v>
       </c>
       <c r="U58" s="4">
-        <f t="shared" ref="U58:W58" si="48">+U22</f>
+        <f t="shared" ref="U58:W58" si="52">+U22</f>
         <v>18485</v>
       </c>
       <c r="V58" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>29146</v>
       </c>
       <c r="W58" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="52"/>
         <v>39370</v>
       </c>
       <c r="X58" s="4">
-        <f t="shared" ref="X58:Y58" si="49">+X22</f>
+        <f t="shared" ref="X58:Y58" si="53">+X22</f>
         <v>23200</v>
       </c>
       <c r="Y58" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="53"/>
         <v>39098</v>
       </c>
       <c r="Z58" s="4">
@@ -12950,23 +13022,23 @@
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
       <c r="T71" s="4">
-        <f t="shared" ref="T71:X71" si="50">+SUM(T65:T70)</f>
+        <f t="shared" ref="T71:X71" si="54">+SUM(T65:T70)</f>
         <v>-1527</v>
       </c>
       <c r="U71" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>7250</v>
       </c>
       <c r="V71" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>-2723</v>
       </c>
       <c r="W71" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>700</v>
       </c>
       <c r="X71" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>5683</v>
       </c>
       <c r="Y71" s="4">
@@ -13108,27 +13180,27 @@
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
       <c r="T72" s="13">
-        <f t="shared" ref="T72:Y72" si="51">+T58+SUM(T59:T64)+T71</f>
+        <f t="shared" ref="T72:Y72" si="55">+T58+SUM(T59:T64)+T71</f>
         <v>29274</v>
       </c>
       <c r="U72" s="13">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>36314</v>
       </c>
       <c r="V72" s="13">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>38747</v>
       </c>
       <c r="W72" s="13">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>57683</v>
       </c>
       <c r="X72" s="13">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>50475</v>
       </c>
       <c r="Y72" s="13">
-        <f t="shared" si="51"/>
+        <f t="shared" si="55"/>
         <v>71113</v>
       </c>
       <c r="Z72" s="13">
@@ -14025,27 +14097,27 @@
       <c r="R78" s="4"/>
       <c r="S78" s="4"/>
       <c r="T78" s="13">
-        <f t="shared" ref="T78:Y78" si="52">+SUM(T73:T77)</f>
+        <f t="shared" ref="T78:Y78" si="56">+SUM(T73:T77)</f>
         <v>-11603</v>
       </c>
       <c r="U78" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-19864</v>
       </c>
       <c r="V78" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-30059</v>
       </c>
       <c r="W78" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-7570</v>
       </c>
       <c r="X78" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-28970</v>
       </c>
       <c r="Y78" s="13">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>-24495</v>
       </c>
       <c r="Z78" s="13">
@@ -15086,19 +15158,19 @@
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
       <c r="T85" s="13">
-        <f t="shared" ref="T85:W85" si="53">+SUM(T79:T84)</f>
+        <f t="shared" ref="T85:W85" si="57">+SUM(T79:T84)</f>
         <v>-15572</v>
       </c>
       <c r="U85" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>-7299</v>
       </c>
       <c r="V85" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>-10292</v>
       </c>
       <c r="W85" s="13">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>-50728</v>
       </c>
       <c r="X85" s="13">
@@ -15394,27 +15466,27 @@
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
       <c r="T87" s="13">
-        <f t="shared" ref="T87:Y87" si="54">+T85+T86+T78+T72</f>
+        <f t="shared" ref="T87:Y87" si="58">+T85+T86+T78+T72</f>
         <v>1920</v>
       </c>
       <c r="U87" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>9155</v>
       </c>
       <c r="V87" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>-1325</v>
       </c>
       <c r="W87" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>-1089</v>
       </c>
       <c r="X87" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>-1269</v>
       </c>
       <c r="Y87" s="13">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>27231</v>
       </c>
       <c r="Z87" s="13">
@@ -15552,27 +15624,27 @@
       <c r="R88" s="4"/>
       <c r="S88" s="4"/>
       <c r="T88" s="4">
-        <f t="shared" ref="T88:Y88" si="55">+T89-T87</f>
+        <f t="shared" ref="T88:Y88" si="59">+T89-T87</f>
         <v>8204</v>
       </c>
       <c r="U88" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>10124</v>
       </c>
       <c r="V88" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>19279</v>
       </c>
       <c r="W88" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>17954</v>
       </c>
       <c r="X88" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>16865</v>
       </c>
       <c r="Y88" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="59"/>
         <v>15596</v>
       </c>
       <c r="Z88" s="4">
@@ -15708,27 +15780,27 @@
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
       <c r="T89" s="4">
-        <f t="shared" ref="T89:Y89" si="56">+U88</f>
+        <f t="shared" ref="T89:Y89" si="60">+U88</f>
         <v>10124</v>
       </c>
       <c r="U89" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>19279</v>
       </c>
       <c r="V89" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>17954</v>
       </c>
       <c r="W89" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>16865</v>
       </c>
       <c r="X89" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>15596</v>
       </c>
       <c r="Y89" s="4">
-        <f t="shared" si="56"/>
+        <f t="shared" si="60"/>
         <v>42827</v>
       </c>
       <c r="Z89" s="4">
@@ -54716,14 +54788,14 @@
       </c>
       <c r="J3" s="33">
         <f>+Main!I2</f>
-        <v>606.92999999999995</v>
+        <v>535</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>249</v>
       </c>
       <c r="O3" s="33">
         <f>+J3</f>
-        <v>606.92999999999995</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
@@ -54732,14 +54804,14 @@
       </c>
       <c r="E4" s="34">
         <f ca="1">+TODAY()</f>
-        <v>46142</v>
+        <v>46233</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>251</v>
       </c>
       <c r="J4" s="35">
         <f ca="1">V62</f>
-        <v>420.08410501503181</v>
+        <v>408.82166587975041</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>252</v>
@@ -54761,7 +54833,7 @@
       </c>
       <c r="J5" s="37">
         <f ca="1">J4/J3-1</f>
-        <v>-0.30785411000439611</v>
+        <v>-0.23584735349579367</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>254</v>
@@ -56265,43 +56337,43 @@
       <c r="L52" s="61"/>
       <c r="M52" s="61">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>21220.300257663832</v>
+        <v>36261.135698821447</v>
       </c>
       <c r="N52" s="61">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>62287.973391030748</v>
+        <v>60821.346355321177</v>
       </c>
       <c r="O52" s="61">
         <f t="shared" ref="O52:U52" ca="1" si="15">O51/(1+$E$18)^O53</f>
-        <v>60576.354859321902</v>
+        <v>59150.02944006832</v>
       </c>
       <c r="P52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>59321.685028141168</v>
+        <v>57924.90195221841</v>
       </c>
       <c r="Q52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>57777.91493351783</v>
+        <v>56417.481329803457</v>
       </c>
       <c r="R52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>54678.152768660089</v>
+        <v>53390.705886904216</v>
       </c>
       <c r="S52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>51540.963611177329</v>
+        <v>50327.384703992007</v>
       </c>
       <c r="T52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>48410.93731640745</v>
+        <v>47271.057727669555</v>
       </c>
       <c r="U52" s="61">
         <f t="shared" ca="1" si="15"/>
-        <v>45324.888984174577</v>
+        <v>44257.673212722024</v>
       </c>
       <c r="V52" s="62">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>42312.454518946637</v>
+        <v>41316.169259268332</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -56310,43 +56382,43 @@
       </c>
       <c r="M53" s="14">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.33333333333333331</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="N53" s="14">
         <f ca="1">M53+1</f>
-        <v>1.3333333333333333</v>
+        <v>1.5833333333333335</v>
       </c>
       <c r="O53" s="14">
         <f ca="1">N53+1</f>
-        <v>2.333333333333333</v>
+        <v>2.5833333333333335</v>
       </c>
       <c r="P53" s="14">
         <f t="shared" ref="P53:V53" ca="1" si="16">O53+1</f>
-        <v>3.333333333333333</v>
+        <v>3.5833333333333335</v>
       </c>
       <c r="Q53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>4.333333333333333</v>
+        <v>4.5833333333333339</v>
       </c>
       <c r="R53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>5.333333333333333</v>
+        <v>5.5833333333333339</v>
       </c>
       <c r="S53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>6.333333333333333</v>
+        <v>6.5833333333333339</v>
       </c>
       <c r="T53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>7.333333333333333</v>
+        <v>7.5833333333333339</v>
       </c>
       <c r="U53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>8.3333333333333321</v>
+        <v>8.5833333333333339</v>
       </c>
       <c r="V53" s="14">
         <f t="shared" ca="1" si="16"/>
-        <v>9.3333333333333321</v>
+        <v>9.5833333333333339</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -56359,7 +56431,7 @@
       <c r="Q54" s="24"/>
       <c r="V54" s="4">
         <f ca="1">SUM(M52:V52)</f>
-        <v>503451.62566904159</v>
+        <v>507137.8855667889</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -56403,7 +56475,7 @@
       <c r="U56" s="63"/>
       <c r="V56" s="64">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>540467.65614109836</v>
+        <v>527741.85317674535</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -56431,7 +56503,7 @@
       <c r="U57" s="65"/>
       <c r="V57" s="66">
         <f ca="1">V54+V56</f>
-        <v>1043919.28181014</v>
+        <v>1034879.7387435343</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -56444,7 +56516,7 @@
       <c r="Q58" s="24"/>
       <c r="V58" s="67">
         <f>+Main!I5</f>
-        <v>81180</v>
+        <v>90260</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.2">
@@ -56472,7 +56544,7 @@
       <c r="U59" s="63"/>
       <c r="V59" s="64">
         <f>+Main!I6</f>
-        <v>58748</v>
+        <v>83664</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.2">
@@ -56485,7 +56557,7 @@
       <c r="Q60" s="24"/>
       <c r="V60" s="67">
         <f ca="1">V57+V58-V59</f>
-        <v>1066351.28181014</v>
+        <v>1041475.7387435343</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -56513,7 +56585,7 @@
       <c r="U61" s="63"/>
       <c r="V61" s="64">
         <f>+Main!I3</f>
-        <v>2538.4233039999999</v>
+        <v>2547.5062250000001</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.2">
@@ -56522,7 +56594,7 @@
       </c>
       <c r="V62" s="67">
         <f ca="1">V60/V61</f>
-        <v>420.08410501503181</v>
+        <v>408.82166587975041</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -56555,35 +56627,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="68"/>
-      <c r="C68" s="75" t="s">
+      <c r="C68" s="76" t="s">
         <v>266</v>
       </c>
-      <c r="D68" s="75"/>
-      <c r="E68" s="75"/>
-      <c r="F68" s="75"/>
-      <c r="G68" s="75"/>
-      <c r="H68" s="75"/>
-      <c r="I68" s="75"/>
-      <c r="J68" s="76"/>
+      <c r="D68" s="76"/>
+      <c r="E68" s="76"/>
+      <c r="F68" s="76"/>
+      <c r="G68" s="76"/>
+      <c r="H68" s="76"/>
+      <c r="I68" s="76"/>
+      <c r="J68" s="77"/>
       <c r="M68" s="68"/>
-      <c r="N68" s="77" t="s">
+      <c r="N68" s="78" t="s">
         <v>294</v>
       </c>
-      <c r="O68" s="77"/>
-      <c r="P68" s="77"/>
-      <c r="Q68" s="77"/>
-      <c r="R68" s="77"/>
-      <c r="S68" s="77"/>
-      <c r="T68" s="77"/>
-      <c r="U68" s="78"/>
+      <c r="O68" s="78"/>
+      <c r="P68" s="78"/>
+      <c r="Q68" s="78"/>
+      <c r="R68" s="78"/>
+      <c r="S68" s="78"/>
+      <c r="T68" s="78"/>
+      <c r="U68" s="79"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="79" t="s">
+      <c r="B69" s="80" t="s">
         <v>156</v>
       </c>
       <c r="C69" s="69">
         <f ca="1">+J4</f>
-        <v>420.08410501503181</v>
+        <v>408.82166587975041</v>
       </c>
       <c r="D69" s="70"/>
       <c r="E69" s="70"/>
@@ -56592,12 +56664,12 @@
       <c r="H69" s="70"/>
       <c r="I69" s="70"/>
       <c r="J69" s="70"/>
-      <c r="M69" s="79" t="s">
+      <c r="M69" s="80" t="s">
         <v>156</v>
       </c>
       <c r="N69" s="69">
         <f ca="1">+J4</f>
-        <v>420.08410501503181</v>
+        <v>408.82166587975041</v>
       </c>
       <c r="O69" s="70"/>
       <c r="P69" s="70"/>
@@ -56608,7 +56680,7 @@
       <c r="U69" s="70"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="79"/>
+      <c r="B70" s="80"/>
       <c r="C70" s="71"/>
       <c r="D70" s="72"/>
       <c r="E70" s="72"/>
@@ -56617,7 +56689,7 @@
       <c r="H70" s="72"/>
       <c r="I70" s="72"/>
       <c r="J70" s="72"/>
-      <c r="M70" s="79"/>
+      <c r="M70" s="80"/>
       <c r="N70" s="71"/>
       <c r="O70" s="72"/>
       <c r="P70" s="72"/>
@@ -56628,7 +56700,7 @@
       <c r="U70" s="72"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="79"/>
+      <c r="B71" s="80"/>
       <c r="C71" s="71"/>
       <c r="D71" s="72"/>
       <c r="E71" s="72"/>
@@ -56637,7 +56709,7 @@
       <c r="H71" s="72"/>
       <c r="I71" s="72"/>
       <c r="J71" s="72"/>
-      <c r="M71" s="79"/>
+      <c r="M71" s="80"/>
       <c r="N71" s="71"/>
       <c r="O71" s="72"/>
       <c r="P71" s="72"/>
@@ -56648,7 +56720,7 @@
       <c r="U71" s="72"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="79"/>
+      <c r="B72" s="80"/>
       <c r="C72" s="71"/>
       <c r="D72" s="73"/>
       <c r="E72" s="73"/>
@@ -56657,7 +56729,7 @@
       <c r="H72" s="73"/>
       <c r="I72" s="73"/>
       <c r="J72" s="73"/>
-      <c r="M72" s="79"/>
+      <c r="M72" s="80"/>
       <c r="N72" s="71"/>
       <c r="O72" s="73"/>
       <c r="P72" s="73"/>
@@ -56668,7 +56740,7 @@
       <c r="U72" s="73"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="79"/>
+      <c r="B73" s="80"/>
       <c r="C73" s="71"/>
       <c r="D73" s="72"/>
       <c r="E73" s="72"/>
@@ -56677,7 +56749,7 @@
       <c r="H73" s="72"/>
       <c r="I73" s="72"/>
       <c r="J73" s="72"/>
-      <c r="M73" s="79"/>
+      <c r="M73" s="80"/>
       <c r="N73" s="71"/>
       <c r="O73" s="72"/>
       <c r="P73" s="72"/>
@@ -56688,7 +56760,7 @@
       <c r="U73" s="72"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="79"/>
+      <c r="B74" s="80"/>
       <c r="C74" s="71"/>
       <c r="D74" s="72"/>
       <c r="E74" s="72"/>
@@ -56697,7 +56769,7 @@
       <c r="H74" s="72"/>
       <c r="I74" s="72"/>
       <c r="J74" s="72"/>
-      <c r="M74" s="79"/>
+      <c r="M74" s="80"/>
       <c r="N74" s="71"/>
       <c r="O74" s="72"/>
       <c r="P74" s="72"/>
@@ -56708,7 +56780,7 @@
       <c r="U74" s="72"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="79"/>
+      <c r="B75" s="80"/>
       <c r="C75" s="71"/>
       <c r="D75" s="72"/>
       <c r="E75" s="72"/>
@@ -56717,7 +56789,7 @@
       <c r="H75" s="72"/>
       <c r="I75" s="72"/>
       <c r="J75" s="72"/>
-      <c r="M75" s="79"/>
+      <c r="M75" s="80"/>
       <c r="N75" s="71"/>
       <c r="O75" s="72"/>
       <c r="P75" s="72"/>
@@ -56728,7 +56800,7 @@
       <c r="U75" s="72"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="80"/>
+      <c r="B76" s="81"/>
       <c r="C76" s="71"/>
       <c r="D76" s="72"/>
       <c r="E76" s="72"/>
@@ -56737,7 +56809,7 @@
       <c r="H76" s="72"/>
       <c r="I76" s="72"/>
       <c r="J76" s="72"/>
-      <c r="M76" s="80"/>
+      <c r="M76" s="81"/>
       <c r="N76" s="71"/>
       <c r="O76" s="72"/>
       <c r="P76" s="72"/>
